--- a/서버정보/20260811_리소스배포_운영.xlsx
+++ b/서버정보/20260811_리소스배포_운영.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F93A0C5-463F-46F0-8131-EB5FF6572BE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F342D02-709C-4139-8F61-017EDE55AAFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1661,7 +1661,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7112" uniqueCount="1065">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7112" uniqueCount="1067">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5565,6 +5565,14 @@
   </si>
   <si>
     <t>p-puls-ap-sbn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>az-p-int-host3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>az-p-int-host4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -25126,7 +25134,7 @@
         <v>24</v>
       </c>
       <c r="F138" s="95" t="s">
-        <v>1057</v>
+        <v>1065</v>
       </c>
       <c r="G138" s="95" t="s">
         <v>1061</v>
@@ -25154,7 +25162,7 @@
       </c>
       <c r="O138" s="115" t="str">
         <f>SUBSTITUTE(F138,"hazr-","")&amp;"-osdisk"</f>
-        <v>az-p-int-host1-osdisk</v>
+        <v>az-p-int-host3-osdisk</v>
       </c>
       <c r="P138" s="116">
         <v>64</v>
@@ -25167,7 +25175,7 @@
       <c r="T138" s="95"/>
       <c r="U138" s="95" t="str">
         <f>SUBSTITUTE(F138,"hazr-","")&amp;"-nic"</f>
-        <v>az-p-int-host1-nic</v>
+        <v>az-p-int-host3-nic</v>
       </c>
       <c r="V138" s="95" t="b">
         <v>1</v>
@@ -25194,7 +25202,7 @@
         <v>318</v>
       </c>
       <c r="AD138" s="74">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE138" s="95"/>
       <c r="AF138" s="95"/>
@@ -25213,7 +25221,7 @@
         <v>24</v>
       </c>
       <c r="F139" s="95" t="s">
-        <v>1058</v>
+        <v>1066</v>
       </c>
       <c r="G139" s="95" t="s">
         <v>1062</v>
@@ -25241,7 +25249,7 @@
       </c>
       <c r="O139" s="115" t="str">
         <f>SUBSTITUTE(F139,"hazr-","")&amp;"-osdisk"</f>
-        <v>az-p-int-host2-osdisk</v>
+        <v>az-p-int-host4-osdisk</v>
       </c>
       <c r="P139" s="116">
         <v>64</v>
@@ -25254,7 +25262,7 @@
       <c r="T139" s="95"/>
       <c r="U139" s="95" t="str">
         <f>SUBSTITUTE(F139,"hazr-","")&amp;"-nic"</f>
-        <v>az-p-int-host2-nic</v>
+        <v>az-p-int-host4-nic</v>
       </c>
       <c r="V139" s="95" t="b">
         <v>1</v>
@@ -25281,7 +25289,7 @@
         <v>318</v>
       </c>
       <c r="AD139" s="74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE139" s="95"/>
       <c r="AF139" s="95"/>
@@ -39286,7 +39294,7 @@
       </c>
       <c r="E156" s="73" t="str">
         <f t="shared" si="6"/>
-        <v>az-p-int-host1-nsg</v>
+        <v>az-p-int-host3-nsg</v>
       </c>
       <c r="F156" s="73" t="s">
         <v>317</v>
@@ -39298,14 +39306,14 @@
         <v>1064</v>
       </c>
       <c r="I156" s="120" t="s">
-        <v>1057</v>
+        <v>1065</v>
       </c>
       <c r="J156" s="120" t="s">
         <v>1056</v>
       </c>
       <c r="K156" s="73" t="str">
         <f t="shared" si="4"/>
-        <v>az-p-int-host1-nic</v>
+        <v>az-p-int-host3-nic</v>
       </c>
       <c r="L156" s="120" t="s">
         <v>226</v>
@@ -39324,7 +39332,7 @@
       </c>
       <c r="E157" s="74" t="str">
         <f t="shared" si="6"/>
-        <v>az-p-int-host2-nsg</v>
+        <v>az-p-int-host4-nsg</v>
       </c>
       <c r="F157" s="74" t="s">
         <v>317</v>
@@ -39336,14 +39344,14 @@
         <v>1064</v>
       </c>
       <c r="I157" s="121" t="s">
-        <v>1058</v>
+        <v>1066</v>
       </c>
       <c r="J157" s="121" t="s">
         <v>1056</v>
       </c>
       <c r="K157" s="74" t="str">
         <f t="shared" si="4"/>
-        <v>az-p-int-host2-nic</v>
+        <v>az-p-int-host4-nic</v>
       </c>
       <c r="L157" s="121" t="s">
         <v>226</v>
@@ -46236,12 +46244,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -46389,15 +46394,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -46421,17 +46437,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260811_리소스배포_운영.xlsx
+++ b/서버정보/20260811_리소스배포_운영.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F342D02-709C-4139-8F61-017EDE55AAFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C33C7B09-1499-4FDE-B7AB-2AEF59901AE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -1661,7 +1661,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7112" uniqueCount="1067">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7112" uniqueCount="1068">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5560,10 +5560,6 @@
     <t>10.158.147.7</t>
   </si>
   <si>
-    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.8_Base_Image/versions/0.0.4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>p-puls-ap-sbn</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5573,6 +5569,13 @@
   </si>
   <si>
     <t>az-p-int-host4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/subscriptions/38befed7-7726-4784-910e-0cea5422077d/resourceGroups/hazr-d-dch-rg/providers/Microsoft.Compute/galleries/temp_ertest_gallery/images/temp_ertest_vm_image/versions/0.0.2</t>
+  </si>
+  <si>
+    <t>/subscriptions/38befed7-7726-4784-910e-0cea5422077d/resourceGroups/hazr-d-dch-rg/providers/Microsoft.Compute/galleries/temp_ertest_gallery/images/temp_ertest_vm_image/versions/0.0.2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -24984,7 +24987,7 @@
         <v>992</v>
       </c>
       <c r="N136" s="119" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="O136" s="115" t="str">
         <f>SUBSTITUTE(F136,"hazr-","")&amp;"-osdisk"</f>
@@ -25016,7 +25019,7 @@
         <v>338</v>
       </c>
       <c r="Z136" s="95" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="AA136" s="95" t="b">
         <v>1</v>
@@ -25071,7 +25074,7 @@
         <v>992</v>
       </c>
       <c r="N137" s="119" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="O137" s="115" t="str">
         <f>SUBSTITUTE(F137,"hazr-","")&amp;"-osdisk"</f>
@@ -25103,7 +25106,7 @@
         <v>338</v>
       </c>
       <c r="Z137" s="95" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="AA137" s="95" t="b">
         <v>1</v>
@@ -25134,7 +25137,7 @@
         <v>24</v>
       </c>
       <c r="F138" s="95" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="G138" s="95" t="s">
         <v>1061</v>
@@ -25158,7 +25161,7 @@
         <v>992</v>
       </c>
       <c r="N138" s="119" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="O138" s="115" t="str">
         <f>SUBSTITUTE(F138,"hazr-","")&amp;"-osdisk"</f>
@@ -25190,7 +25193,7 @@
         <v>338</v>
       </c>
       <c r="Z138" s="95" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="AA138" s="95" t="b">
         <v>1</v>
@@ -25221,7 +25224,7 @@
         <v>24</v>
       </c>
       <c r="F139" s="95" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="G139" s="95" t="s">
         <v>1062</v>
@@ -25245,7 +25248,7 @@
         <v>992</v>
       </c>
       <c r="N139" s="119" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="O139" s="115" t="str">
         <f>SUBSTITUTE(F139,"hazr-","")&amp;"-osdisk"</f>
@@ -25277,7 +25280,7 @@
         <v>338</v>
       </c>
       <c r="Z139" s="95" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="AA139" s="95" t="b">
         <v>1</v>
@@ -39227,7 +39230,7 @@
         <v>338</v>
       </c>
       <c r="H154" s="120" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I154" s="120" t="s">
         <v>1057</v>
@@ -39265,7 +39268,7 @@
         <v>338</v>
       </c>
       <c r="H155" s="121" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I155" s="121" t="s">
         <v>1058</v>
@@ -39303,10 +39306,10 @@
         <v>338</v>
       </c>
       <c r="H156" s="120" t="s">
+        <v>1063</v>
+      </c>
+      <c r="I156" s="120" t="s">
         <v>1064</v>
-      </c>
-      <c r="I156" s="120" t="s">
-        <v>1065</v>
       </c>
       <c r="J156" s="120" t="s">
         <v>1056</v>
@@ -39341,10 +39344,10 @@
         <v>338</v>
       </c>
       <c r="H157" s="121" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I157" s="121" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="J157" s="121" t="s">
         <v>1056</v>
@@ -46244,9 +46247,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -46394,26 +46400,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -46437,9 +46432,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260811_리소스배포_운영.xlsx
+++ b/서버정보/20260811_리소스배포_운영.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C33C7B09-1499-4FDE-B7AB-2AEF59901AE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5136783-D006-4117-B191-EFED69AF1859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1661,7 +1661,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7112" uniqueCount="1068">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7112" uniqueCount="1067">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5572,10 +5572,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>/subscriptions/38befed7-7726-4784-910e-0cea5422077d/resourceGroups/hazr-d-dch-rg/providers/Microsoft.Compute/galleries/temp_ertest_gallery/images/temp_ertest_vm_image/versions/0.0.2</t>
-  </si>
-  <si>
-    <t>/subscriptions/38befed7-7726-4784-910e-0cea5422077d/resourceGroups/hazr-d-dch-rg/providers/Microsoft.Compute/galleries/temp_ertest_gallery/images/temp_ertest_vm_image/versions/0.0.2</t>
+    <t>/subscriptions/38befed7-7226-4784-910e-0cea5422077d/resourceGroups/hazr-d-dch-rg/providers/Microsoft.Compute/galleries/temp_ertest_gallery/images/temp_ertest_vm_image/versions/0.0.2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -24986,7 +24983,7 @@
       <c r="M136" s="95" t="s">
         <v>992</v>
       </c>
-      <c r="N136" s="119" t="s">
+      <c r="N136" s="1" t="s">
         <v>1066</v>
       </c>
       <c r="O136" s="115" t="str">
@@ -25073,8 +25070,8 @@
       <c r="M137" s="95" t="s">
         <v>992</v>
       </c>
-      <c r="N137" s="119" t="s">
-        <v>1067</v>
+      <c r="N137" s="1" t="s">
+        <v>1066</v>
       </c>
       <c r="O137" s="115" t="str">
         <f>SUBSTITUTE(F137,"hazr-","")&amp;"-osdisk"</f>
@@ -25160,8 +25157,8 @@
       <c r="M138" s="95" t="s">
         <v>992</v>
       </c>
-      <c r="N138" s="119" t="s">
-        <v>1067</v>
+      <c r="N138" s="1" t="s">
+        <v>1066</v>
       </c>
       <c r="O138" s="115" t="str">
         <f>SUBSTITUTE(F138,"hazr-","")&amp;"-osdisk"</f>
@@ -25247,8 +25244,8 @@
       <c r="M139" s="95" t="s">
         <v>992</v>
       </c>
-      <c r="N139" s="119" t="s">
-        <v>1067</v>
+      <c r="N139" s="1" t="s">
+        <v>1066</v>
       </c>
       <c r="O139" s="115" t="str">
         <f>SUBSTITUTE(F139,"hazr-","")&amp;"-osdisk"</f>
@@ -46256,6 +46253,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -46399,12 +46402,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
@@ -46414,6 +46411,22 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -46429,20 +46442,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>